--- a/data/trans_orig/IQ28_P-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_P-Estudios-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Peso medio, en kilogramos, recogido tras medición</t>
+          <t>Peso medio, en kilogramos, recogido tras medición (tasa de respuesta: 93,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,72; 39,48</t>
+          <t>33,57; 39,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,91; 39,48</t>
+          <t>32,59; 39,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41,63; 50,49</t>
+          <t>41,49; 50,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33,63; 40,38</t>
+          <t>33,77; 40,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,24; 40,07</t>
+          <t>33,23; 40,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,18; 45,38</t>
+          <t>32,06; 45,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,5; 38,79</t>
+          <t>34,6; 39,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>33,97; 39,08</t>
+          <t>33,95; 39,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>37,91; 46,57</t>
+          <t>37,42; 46,13</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,26; 35,97</t>
+          <t>33,31; 35,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33,92; 36,39</t>
+          <t>34,0; 36,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,87; 47,22</t>
+          <t>34,99; 47,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34,5; 37,25</t>
+          <t>34,57; 37,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,91; 36,39</t>
+          <t>33,81; 36,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,42; 44,98</t>
+          <t>39,4; 44,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,25; 36,24</t>
+          <t>34,27; 36,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,35; 36,15</t>
+          <t>34,34; 36,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38,64; 45,75</t>
+          <t>38,32; 45,0</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,25; 33,4</t>
+          <t>29,17; 33,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29,09; 33,4</t>
+          <t>29,08; 33,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32,6; 39,32</t>
+          <t>33,1; 39,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31,14; 35,86</t>
+          <t>31,07; 36,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,48; 36,32</t>
+          <t>31,4; 35,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,82; 41,6</t>
+          <t>34,38; 41,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,95; 33,96</t>
+          <t>30,86; 34,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,93; 34,05</t>
+          <t>30,87; 34,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34,9; 39,67</t>
+          <t>34,94; 39,74</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33,02; 35,16</t>
+          <t>33,07; 35,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33,25; 35,31</t>
+          <t>33,28; 35,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,36; 46,22</t>
+          <t>36,32; 46,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34,3; 36,62</t>
+          <t>34,45; 36,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,92; 36,02</t>
+          <t>33,95; 36,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,76; 42,84</t>
+          <t>38,64; 42,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,97; 35,53</t>
+          <t>34,04; 35,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33,94; 35,45</t>
+          <t>33,88; 35,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,18; 42,86</t>
+          <t>38,22; 43,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ28_P-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_P-Estudios-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Peso medio, en kilogramos, recogido tras medición (tasa de respuesta: 93,67%)</t>
+          <t>Peso medio, en kilogramos, recogido por medición (tasa de respuesta: 93,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,57; 39,19</t>
+          <t>33,71; 39,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,59; 39,47</t>
+          <t>32,37; 39,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41,49; 50,28</t>
+          <t>41,53; 50,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33,77; 40,48</t>
+          <t>33,82; 40,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,23; 40,21</t>
+          <t>33,24; 40,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,06; 45,72</t>
+          <t>31,88; 45,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,6; 39,14</t>
+          <t>34,62; 38,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>33,95; 39,1</t>
+          <t>34,1; 39,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>37,42; 46,13</t>
+          <t>38,31; 46,84</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,31; 35,99</t>
+          <t>33,26; 35,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34,0; 36,51</t>
+          <t>34,01; 36,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,99; 47,69</t>
+          <t>35,29; 49,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34,57; 37,39</t>
+          <t>34,46; 37,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,81; 36,56</t>
+          <t>33,83; 36,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,4; 44,77</t>
+          <t>39,4; 44,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,27; 36,28</t>
+          <t>34,3; 36,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,34; 36,1</t>
+          <t>34,26; 36,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38,32; 45,0</t>
+          <t>38,66; 45,5</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,17; 33,38</t>
+          <t>29,31; 33,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29,08; 33,57</t>
+          <t>29,29; 33,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33,1; 39,61</t>
+          <t>32,93; 39,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31,07; 36,17</t>
+          <t>31,11; 35,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,4; 35,93</t>
+          <t>31,58; 36,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,38; 41,85</t>
+          <t>35,01; 42,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,86; 34,07</t>
+          <t>30,9; 33,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,87; 34,02</t>
+          <t>30,92; 33,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34,94; 39,74</t>
+          <t>35,0; 39,59</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33,07; 35,17</t>
+          <t>32,85; 35,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33,28; 35,26</t>
+          <t>33,24; 35,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,32; 46,27</t>
+          <t>36,36; 46,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34,45; 36,74</t>
+          <t>34,31; 36,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,95; 36,18</t>
+          <t>33,86; 36,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,64; 42,94</t>
+          <t>38,81; 42,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,04; 35,58</t>
+          <t>34,01; 35,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33,88; 35,38</t>
+          <t>33,9; 35,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,22; 43,12</t>
+          <t>38,37; 43,55</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ28_P-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_P-Estudios-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>36,97</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>36,66</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>39,88</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>36,39</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>35,89</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>46,38</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>36,97</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>36,66</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,15</t>
+          <t>46,18</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>42,02</t>
+          <t>42,65</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,71; 39,49</t>
+          <t>33,63; 40,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,37; 39,68</t>
+          <t>33,24; 40,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41,53; 50,42</t>
+          <t>33,74; 47,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33,82; 40,37</t>
+          <t>33,72; 39,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,24; 40,48</t>
+          <t>32,91; 39,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,88; 45,47</t>
+          <t>40,81; 51,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,62; 38,97</t>
+          <t>34,5; 38,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,1; 39,19</t>
+          <t>33,97; 39,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>38,31; 46,84</t>
+          <t>38,22; 47,22</t>
         </is>
       </c>
     </row>
@@ -734,47 +734,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>35,83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>35,18</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>42,64</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>34,6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>35,18</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>39,63</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>35,83</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>37,07</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>35,24</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>35,18</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>41,84</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>35,24</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>35,18</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>40,85</t>
+          <t>40,24</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,26; 35,95</t>
+          <t>34,5; 37,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34,01; 36,51</t>
+          <t>33,91; 36,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35,29; 49,7</t>
+          <t>40,33; 45,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34,46; 37,25</t>
+          <t>33,26; 35,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,83; 36,62</t>
+          <t>33,92; 36,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,4; 44,66</t>
+          <t>34,81; 39,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,3; 36,26</t>
+          <t>34,25; 36,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,26; 36,12</t>
+          <t>34,35; 36,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38,66; 45,5</t>
+          <t>38,61; 42,07</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>33,56</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>33,69</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>39,12</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>31,23</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>31,16</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>36,09</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>33,56</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>33,69</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,22</t>
+          <t>36,81</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>37,23</t>
+          <t>38,0</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,31; 33,24</t>
+          <t>31,14; 35,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29,29; 33,23</t>
+          <t>31,48; 36,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32,93; 39,48</t>
+          <t>35,72; 42,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31,11; 35,89</t>
+          <t>29,25; 33,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,58; 36,27</t>
+          <t>29,09; 33,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,01; 42,25</t>
+          <t>33,58; 40,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,9; 33,93</t>
+          <t>30,95; 33,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,92; 33,99</t>
+          <t>30,93; 34,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>35,0; 39,59</t>
+          <t>35,65; 40,67</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>35,47</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>34,98</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>41,57</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>34,06</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>34,29</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>39,33</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>35,47</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>34,98</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,67</t>
+          <t>37,7</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>40,06</t>
+          <t>39,85</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32,85; 35,06</t>
+          <t>34,3; 36,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33,24; 35,3</t>
+          <t>33,92; 36,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,36; 46,79</t>
+          <t>39,65; 43,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34,31; 36,57</t>
+          <t>33,02; 35,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,86; 36,12</t>
+          <t>33,25; 35,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,81; 42,98</t>
+          <t>35,95; 39,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,01; 35,53</t>
+          <t>33,97; 35,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33,9; 35,41</t>
+          <t>33,94; 35,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,37; 43,55</t>
+          <t>38,52; 41,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ28_P-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_P-Estudios-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -622,329 +627,217 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>36,97</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>36,66</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>39,88</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>36,39</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>35,89</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>46,18</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>36,67</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>36,32</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>42,65</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>36.97087468140273</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>36.66150752917831</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>39.87915983242575</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>36.38737593417594</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>35.88909012835779</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>46.18106959821151</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>36.67017182631495</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>36.32181606240054</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>42.65260095241134</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>33,63; 40,38</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>33,24; 40,07</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>33,74; 47,23</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>33,72; 39,48</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>32,91; 39,48</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>40,81; 51,09</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>34,5; 38,79</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>33,97; 39,08</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>38,22; 47,22</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>33.63050415274581</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>33.23813712210055</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>33.74258605573727</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>33.71781394263484</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>32.90578080609445</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>40.80618218515858</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>34.49871383562671</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>33.97186617943277</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>38.21907832306067</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>40.38346471270162</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>40.07356069972373</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>47.22799263533622</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>39.48475188374469</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>39.47681237680791</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>51.09347195319321</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>38.79410701513228</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>39.08244678690603</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>47.22045860295066</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>35,83</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>35,18</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>42,64</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>34,6</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>35,18</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>37,07</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>35,24</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>35,18</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>40,24</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>34,5; 37,25</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>33,91; 36,39</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>40,33; 45,66</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>33,26; 35,97</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>33,92; 36,39</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>34,81; 39,48</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>34,25; 36,24</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>34,35; 36,15</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>38,61; 42,07</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>35.8330363907401</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>35.17579964423406</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>42.63878172264589</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>34.59808490695445</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>35.17600688870688</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>37.07000187292152</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>35.2416241521577</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>35.17589948846733</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>40.239859210786</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>33,56</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>33,69</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>39,12</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>31,23</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>31,16</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>36,81</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>32,39</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>32,47</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>38,0</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>34.50371152171678</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>33.91424673471731</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>40.32760483956933</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>33.25573714311108</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>33.91807860822057</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>34.81315709778427</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>34.25393629159731</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>34.35094045189111</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>38.61290130431985</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>31,14; 35,86</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>31,48; 36,32</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>35,72; 42,66</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>29,25; 33,4</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>29,09; 33,4</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>33,58; 40,02</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>30,95; 33,96</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>30,93; 34,05</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>35,65; 40,67</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>37.2453247164005</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>36.39056876397787</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>45.65524521430827</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>35.97398561683929</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>36.39381535359045</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>39.47926079115091</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>36.2432555164072</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>36.15383322689297</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>42.07092811880753</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -952,107 +845,215 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>35,47</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>34,98</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>41,57</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>34,06</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>34,29</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>37,7</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>34,78</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>34,65</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>39,85</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>33.56189996168461</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>33.68600562859044</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>39.117132170159</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>31.2317011614664</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>31.15852611154262</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>36.80522979604564</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>32.39445430221217</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>32.46882725103777</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>38.00337396755543</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>34,3; 36,62</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>33,92; 36,02</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>39,65; 43,6</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>33,02; 35,16</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>33,25; 35,31</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>35,95; 39,55</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>33,97; 35,53</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>33,94; 35,45</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>38,52; 41,33</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>31.13999028195578</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>31.47648777298256</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>35.72451176029423</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>29.24785128050098</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>29.08709801938813</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>33.57521577098733</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>30.95313503309586</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>30.93429455819729</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>35.64596825564319</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>35.85873214038979</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>36.31863258292963</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>42.65511381575137</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>33.39535443251072</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>33.40304929654667</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>40.01584931323178</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>33.96495954581839</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>34.05395336178695</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>40.66632794195122</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>35.46886982453607</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>34.98302810569339</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>41.57133812767115</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>34.05725872658873</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>34.28930529698515</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>37.70141136710089</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>34.77921254206496</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>34.65166167910315</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>39.85043180912425</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>34.29569487224026</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>33.92413600596117</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>39.64719022744256</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>33.01926233159483</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>33.25006435481784</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>35.95337775818846</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>33.97089553246359</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>33.93870104361312</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>38.52149160223204</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>36.61976899260237</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>36.01709270789181</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>43.59954962486894</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>35.16099858478962</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>35.3139747648505</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>39.54557786256876</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>35.52806270251784</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>35.45095558898304</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>41.32859582643594</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1061,13 +1062,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
